--- a/Modules/03-Data-Architect/projects/Project 4 - SneakerPark Data Governance/report/sneakerpark_data_catalog.xlsx
+++ b/Modules/03-Data-Architect/projects/Project 4 - SneakerPark Data Governance/report/sneakerpark_data_catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/be4ab9aaf12c5868/Documents/Github/Udacity-Master-Artificial-Intelligence/udacity-ai-masters/Modules/03-Data-Architect/projects/Project 4 - SneakerPark Data Governance/report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{A062A1EE-BF8D-41F0-9655-A80E3764D7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72D6CF98-6278-4826-A6F4-9AEAD37DB7AF}"/>
+  <xr:revisionPtr revIDLastSave="435" documentId="8_{A062A1EE-BF8D-41F0-9655-A80E3764D7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94304526-3737-41B6-9CEE-E689A4916D8A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Dictionary" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="235">
   <si>
     <t>Entity</t>
   </si>
@@ -480,9 +480,6 @@
     <t>User Service</t>
   </si>
   <si>
-    <t>usr.users</t>
-  </si>
-  <si>
     <t>UserID</t>
   </si>
   <si>
@@ -492,435 +489,222 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Stores UserID information for users.</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
     <t>FirstName</t>
   </si>
   <si>
-    <t>VARCHAR</t>
-  </si>
-  <si>
-    <t>Stores FirstName information for users.</t>
-  </si>
-  <si>
     <t>LastName</t>
   </si>
   <si>
-    <t>Stores LastName information for users.</t>
-  </si>
-  <si>
     <t>Email</t>
   </si>
   <si>
     <t>VARCHAR(50)</t>
   </si>
   <si>
-    <t>Stores Email information for users.</t>
-  </si>
-  <si>
     <t>Address</t>
   </si>
   <si>
-    <t>Stores Address information for users.</t>
-  </si>
-  <si>
     <t>ZipCode</t>
   </si>
   <si>
     <t>VARCHAR(10)</t>
   </si>
   <si>
-    <t>Stores ZipCode information for users.</t>
-  </si>
-  <si>
     <t>creditcards</t>
   </si>
   <si>
-    <t>usr.creditcards</t>
-  </si>
-  <si>
     <t>CreditCardID</t>
   </si>
   <si>
-    <t>Stores CreditCardID information for creditcards.</t>
-  </si>
-  <si>
-    <t>Possible</t>
-  </si>
-  <si>
     <t>CreditCardNumber</t>
   </si>
   <si>
-    <t>Stores CreditCardNumber information for creditcards.</t>
-  </si>
-  <si>
     <t>CreditCardExpirationDate</t>
   </si>
   <si>
     <t>DATE</t>
   </si>
   <si>
-    <t>Stores CreditCardExpirationDate information for creditcards.</t>
-  </si>
-  <si>
-    <t>Stores UserID information for creditcards.</t>
-  </si>
-  <si>
     <t>listings</t>
   </si>
   <si>
     <t>Listing Service</t>
   </si>
   <si>
-    <t>li.listings</t>
-  </si>
-  <si>
     <t>ListingID</t>
   </si>
   <si>
-    <t>Stores ListingID information for listings.</t>
-  </si>
-  <si>
     <t>SellerID</t>
   </si>
   <si>
-    <t>Stores SellerID information for listings.</t>
-  </si>
-  <si>
     <t>ProductID</t>
   </si>
   <si>
-    <t>Stores ProductID information for listings.</t>
-  </si>
-  <si>
     <t>ShoeType</t>
   </si>
   <si>
-    <t>Stores ShoeType information for listings.</t>
-  </si>
-  <si>
     <t>Brand</t>
   </si>
   <si>
-    <t>Stores Brand information for listings.</t>
-  </si>
-  <si>
     <t>Color</t>
   </si>
   <si>
-    <t>Stores Color information for listings.</t>
-  </si>
-  <si>
     <t>Gender</t>
   </si>
   <si>
     <t>CHAR(1)</t>
   </si>
   <si>
-    <t>Stores Gender information for listings.</t>
-  </si>
-  <si>
     <t>Size</t>
   </si>
   <si>
     <t>VARCHAR(4)</t>
   </si>
   <si>
-    <t>Stores Size information for listings.</t>
-  </si>
-  <si>
     <t>Condition</t>
   </si>
   <si>
-    <t>Stores Condition information for listings.</t>
-  </si>
-  <si>
     <t>ListingPrice</t>
   </si>
   <si>
     <t>DECIMAL(8,2)</t>
   </si>
   <si>
-    <t>Stores ListingPrice information for listings.</t>
-  </si>
-  <si>
     <t>ListingType</t>
   </si>
   <si>
     <t>VARCHAR(20)</t>
   </si>
   <si>
-    <t>Stores ListingType information for listings.</t>
-  </si>
-  <si>
     <t>ListingCreateDate</t>
   </si>
   <si>
-    <t>Stores ListingCreateDate information for listings.</t>
-  </si>
-  <si>
     <t>ListingEndDate</t>
   </si>
   <si>
-    <t>Stores ListingEndDate information for listings.</t>
-  </si>
-  <si>
     <t>Orders</t>
   </si>
   <si>
     <t>Order Processing Service</t>
   </si>
   <si>
-    <t>op.Orders</t>
-  </si>
-  <si>
     <t>OrderID</t>
   </si>
   <si>
-    <t>Stores OrderID information for Orders.</t>
-  </si>
-  <si>
     <t>BuyerID</t>
   </si>
   <si>
-    <t>Stores BuyerID information for Orders.</t>
-  </si>
-  <si>
-    <t>Stores CreditCardID information for Orders.</t>
-  </si>
-  <si>
     <t>ShippingCost</t>
   </si>
   <si>
     <t>DECIMAL</t>
   </si>
   <si>
-    <t>Stores ShippingCost information for Orders.</t>
-  </si>
-  <si>
     <t>TaxRatePercent</t>
   </si>
   <si>
     <t>SMALLINT</t>
   </si>
   <si>
-    <t>Stores TaxRatePercent information for Orders.</t>
-  </si>
-  <si>
     <t>TotalAmount</t>
   </si>
   <si>
-    <t>Stores TotalAmount information for Orders.</t>
-  </si>
-  <si>
     <t>ShippingAddress</t>
   </si>
   <si>
     <t>VARCHAR(100)</t>
   </si>
   <si>
-    <t>Stores ShippingAddress information for Orders.</t>
-  </si>
-  <si>
     <t>ShippingZipCode</t>
   </si>
   <si>
-    <t>Stores ShippingZipCode information for Orders.</t>
-  </si>
-  <si>
     <t>OrderDate</t>
   </si>
   <si>
     <t>TIMESTAMP</t>
   </si>
   <si>
-    <t>Stores OrderDate information for Orders.</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Stores Status information for Orders.</t>
-  </si>
-  <si>
     <t>OrderItems</t>
   </si>
   <si>
-    <t>op.OrderItems</t>
-  </si>
-  <si>
-    <t>Stores OrderID information for OrderItems.</t>
-  </si>
-  <si>
-    <t>Stores ListingID information for OrderItems.</t>
-  </si>
-  <si>
     <t>ListingSoldPrice</t>
   </si>
   <si>
-    <t>Stores ListingSoldPrice information for OrderItems.</t>
-  </si>
-  <si>
     <t>OrderShipments</t>
   </si>
   <si>
-    <t>op.OrderShipments</t>
-  </si>
-  <si>
     <t>ShipmentID</t>
   </si>
   <si>
-    <t>Stores ShipmentID information for OrderShipments.</t>
-  </si>
-  <si>
-    <t>Stores OrderID information for OrderShipments.</t>
-  </si>
-  <si>
     <t>Carrier</t>
   </si>
   <si>
-    <t>Stores Carrier information for OrderShipments.</t>
-  </si>
-  <si>
     <t>TrackingNumber</t>
   </si>
   <si>
     <t>VARCHAR(30)</t>
   </si>
   <si>
-    <t>Stores TrackingNumber information for OrderShipments.</t>
-  </si>
-  <si>
     <t>OrderShipDate</t>
   </si>
   <si>
-    <t>Stores OrderShipDate information for OrderShipments.</t>
-  </si>
-  <si>
     <t>Items</t>
   </si>
   <si>
     <t>Inventory Management System</t>
   </si>
   <si>
-    <t>im.Items</t>
-  </si>
-  <si>
     <t>ItemID</t>
   </si>
   <si>
-    <t>Stores ItemID information for Items.</t>
-  </si>
-  <si>
     <t>ItemName</t>
   </si>
   <si>
-    <t>Stores ItemName information for Items.</t>
-  </si>
-  <si>
-    <t>Stores SellerID information for Items.</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Stores Type information for Items.</t>
-  </si>
-  <si>
     <t>BrandName</t>
   </si>
   <si>
-    <t>Stores BrandName information for Items.</t>
-  </si>
-  <si>
     <t>VARCHAR(15)</t>
   </si>
   <si>
-    <t>Stores Color information for Items.</t>
-  </si>
-  <si>
-    <t>Stores Size information for Items.</t>
-  </si>
-  <si>
     <t>Sex</t>
   </si>
   <si>
-    <t>Stores Sex information for Items.</t>
-  </si>
-  <si>
-    <t>Stores Condition information for Items.</t>
-  </si>
-  <si>
     <t>ItemStatus</t>
   </si>
   <si>
-    <t>Stores ItemStatus information for Items.</t>
-  </si>
-  <si>
     <t>ArrivalDate</t>
   </si>
   <si>
-    <t>Stores ArrivalDate information for Items.</t>
-  </si>
-  <si>
     <t>CustomerServiceRequests</t>
   </si>
   <si>
     <t>Customer Service Application</t>
   </si>
   <si>
-    <t>cs.CustomerServiceRequests</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
-    <t>Stores ID information for CustomerServiceRequests.</t>
-  </si>
-  <si>
-    <t>Stores UserID information for CustomerServiceRequests.</t>
-  </si>
-  <si>
-    <t>Stores FirstName information for CustomerServiceRequests.</t>
-  </si>
-  <si>
-    <t>Stores LastName information for CustomerServiceRequests.</t>
-  </si>
-  <si>
     <t>ContactReason</t>
   </si>
   <si>
-    <t>Stores ContactReason information for CustomerServiceRequests.</t>
-  </si>
-  <si>
-    <t>Stores Email information for CustomerServiceRequests.</t>
-  </si>
-  <si>
     <t>Phone</t>
   </si>
   <si>
-    <t>Stores Phone information for CustomerServiceRequests.</t>
-  </si>
-  <si>
-    <t>Stores OrderID information for CustomerServiceRequests.</t>
-  </si>
-  <si>
     <t>Resolution</t>
   </si>
   <si>
-    <t>Stores Resolution information for CustomerServiceRequests.</t>
-  </si>
-  <si>
     <t>ContactMethod</t>
   </si>
   <si>
-    <t>Stores ContactMethod information for CustomerServiceRequests.</t>
-  </si>
-  <si>
     <t>Table</t>
   </si>
   <si>
@@ -951,52 +735,25 @@
     <t>Confidential</t>
   </si>
   <si>
-    <t>Customer Operations Team</t>
-  </si>
-  <si>
     <t>Highly Confidential</t>
   </si>
   <si>
-    <t>Payments Team</t>
-  </si>
-  <si>
     <t>Listings</t>
   </si>
   <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>2 Years Post Expiration</t>
-  </si>
-  <si>
     <t>Internal</t>
   </si>
   <si>
-    <t>Marketplace Operations Team</t>
-  </si>
-  <si>
     <t>Critical</t>
   </si>
   <si>
-    <t>Ecommerce Operations Team</t>
-  </si>
-  <si>
-    <t>Logistics Team</t>
-  </si>
-  <si>
     <t>Inventory</t>
   </si>
   <si>
-    <t>Current State Only</t>
-  </si>
-  <si>
-    <t>Warehouse Operations Team</t>
-  </si>
-  <si>
     <t>Customer Support</t>
-  </si>
-  <si>
-    <t>Customer Support Team</t>
   </si>
   <si>
     <t>Existing Issue</t>
@@ -1103,6 +860,285 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>Basketball</t>
+  </si>
+  <si>
+    <t>Nike</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Buy Now</t>
+  </si>
+  <si>
+    <t>45 Park Avenue</t>
+  </si>
+  <si>
+    <t>2026-01-15 10:15:00</t>
+  </si>
+  <si>
+    <t>Shipped</t>
+  </si>
+  <si>
+    <t>FedEx</t>
+  </si>
+  <si>
+    <t>TRK123456789</t>
+  </si>
+  <si>
+    <t>Air Jordan 1</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Used</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Williams</t>
+  </si>
+  <si>
+    <t>Delayed Shipment</t>
+  </si>
+  <si>
+    <t>sarah@email.com</t>
+  </si>
+  <si>
+    <t>555-123-4567</t>
+  </si>
+  <si>
+    <t>Refund Issued</t>
+  </si>
+  <si>
+    <t>Customer Service Case</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Credit Card</t>
+  </si>
+  <si>
+    <t>Seller Listing</t>
+  </si>
+  <si>
+    <t>Customer Order</t>
+  </si>
+  <si>
+    <t>Order Line</t>
+  </si>
+  <si>
+    <t>Order Shipment</t>
+  </si>
+  <si>
+    <t>Sneaker Item</t>
+  </si>
+  <si>
+    <t>Unique identifier for the customer account</t>
+  </si>
+  <si>
+    <t>Customer first name</t>
+  </si>
+  <si>
+    <t>Customer last name</t>
+  </si>
+  <si>
+    <t>Customer email address</t>
+  </si>
+  <si>
+    <t>Customer mailing address</t>
+  </si>
+  <si>
+    <t>Customer postal zip code</t>
+  </si>
+  <si>
+    <t>Unique identifier for the payment card</t>
+  </si>
+  <si>
+    <t>Customer payment card number</t>
+  </si>
+  <si>
+    <t>Payment card expiration date</t>
+  </si>
+  <si>
+    <t>Customer associated with the payment card</t>
+  </si>
+  <si>
+    <t>Unique identifier for marketplace listing</t>
+  </si>
+  <si>
+    <t>Seller who created the listing</t>
+  </si>
+  <si>
+    <t>Sneaker item associated with listing</t>
+  </si>
+  <si>
+    <t>Type/category of sneake</t>
+  </si>
+  <si>
+    <t>Sneaker brand</t>
+  </si>
+  <si>
+    <t>Sneaker colour</t>
+  </si>
+  <si>
+    <t>Target gender category</t>
+  </si>
+  <si>
+    <t>Sneaker size</t>
+  </si>
+  <si>
+    <t>Sneaker condition</t>
+  </si>
+  <si>
+    <t>Price seller listed item for</t>
+  </si>
+  <si>
+    <t>Listing sale type</t>
+  </si>
+  <si>
+    <t>Date listing was created</t>
+  </si>
+  <si>
+    <t>Listing expiration date</t>
+  </si>
+  <si>
+    <t>Unique identifier for customer order</t>
+  </si>
+  <si>
+    <t>Customer who placed the order</t>
+  </si>
+  <si>
+    <t>Payment card used for the order</t>
+  </si>
+  <si>
+    <t>Shipping cost charged to customer</t>
+  </si>
+  <si>
+    <t>Tax percentage applied to order</t>
+  </si>
+  <si>
+    <t>Total order amount</t>
+  </si>
+  <si>
+    <t>Shipping destination address</t>
+  </si>
+  <si>
+    <t>Shipping postal zip code</t>
+  </si>
+  <si>
+    <t>Date and time order was placed</t>
+  </si>
+  <si>
+    <t>Current order status</t>
+  </si>
+  <si>
+    <t>Customer order associated with the line item</t>
+  </si>
+  <si>
+    <t>Listing purchased in the order</t>
+  </si>
+  <si>
+    <t>Final sold price of listing</t>
+  </si>
+  <si>
+    <t>Unique shipment identifier</t>
+  </si>
+  <si>
+    <t>Customer order linked to shipment</t>
+  </si>
+  <si>
+    <t>Shipment carrier provider</t>
+  </si>
+  <si>
+    <t>Shipment tracking number</t>
+  </si>
+  <si>
+    <t>Date order was shipped</t>
+  </si>
+  <si>
+    <t>Unique sneaker inventory identifier</t>
+  </si>
+  <si>
+    <t>Sneaker product name</t>
+  </si>
+  <si>
+    <t>Seller who submitted sneaker item</t>
+  </si>
+  <si>
+    <t>Sneaker category/type</t>
+  </si>
+  <si>
+    <t>Gender category</t>
+  </si>
+  <si>
+    <t>Current warehouse item status</t>
+  </si>
+  <si>
+    <t>Date item arrived at warehouse</t>
+  </si>
+  <si>
+    <t>Unique customer service request identifier</t>
+  </si>
+  <si>
+    <t>Customer associated with support request</t>
+  </si>
+  <si>
+    <t>Reason customer contacted support</t>
+  </si>
+  <si>
+    <t>Customer contact number</t>
+  </si>
+  <si>
+    <t>Related customer order</t>
+  </si>
+  <si>
+    <t>Resolution outcome for support case</t>
+  </si>
+  <si>
+    <t>Customer communication method</t>
+  </si>
+  <si>
+    <t>Customer Operations Manager</t>
+  </si>
+  <si>
+    <t>Payments Manager</t>
+  </si>
+  <si>
+    <t>2 Years After Listing Expiration</t>
+  </si>
+  <si>
+    <t>Marketplace Operations Manager</t>
+  </si>
+  <si>
+    <t>Ecommerce Operations Manager</t>
+  </si>
+  <si>
+    <t>Logistics Operations Manager</t>
+  </si>
+  <si>
+    <t>Current State Only (No Historical Retention)</t>
+  </si>
+  <si>
+    <t>Warehouse Operations Manager</t>
+  </si>
+  <si>
+    <t>Customer Service Manager</t>
   </si>
 </sst>
 </file>
@@ -1110,9 +1146,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1142,8 +1178,14 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1180,6 +1222,12 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1209,7 +1257,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1240,22 +1288,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1270,6 +1309,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1498,19 +1555,19 @@
   <dimension ref="A1:M507"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.109375" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.109375" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.88671875" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="55.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.21875" style="11" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" style="11" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" style="11" customWidth="1"/>
-    <col min="12" max="12" width="17.88671875" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" customWidth="1"/>
+    <col min="8" max="8" width="38.21875" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
@@ -1556,7 +1613,7 @@
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>14</v>
@@ -1565,39 +1622,39 @@
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="I2" s="2">
         <v>1001</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>14</v>
@@ -1606,39 +1663,39 @@
         <v>13</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>22</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>14</v>
@@ -1647,39 +1704,39 @@
         <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>22</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>219</v>
+        <v>138</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>14</v>
@@ -1688,39 +1745,39 @@
         <v>13</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>220</v>
+        <v>174</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>14</v>
@@ -1729,39 +1786,39 @@
         <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>221</v>
+        <v>140</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>14</v>
@@ -1770,2108 +1827,2436 @@
         <v>13</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="I7" s="8">
         <v>90210</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>222</v>
+        <v>18</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>141</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>177</v>
       </c>
       <c r="I9" s="2">
         <v>5001</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="M9" s="22" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>22</v>
+        <v>28</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>47</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="16">
+        <v>18</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="I10" s="13">
         <v>4111111111111110</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L10" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="17">
+        <v>18</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="I11" s="14">
         <v>46752</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="M11" s="22" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="G12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>44</v>
+        <v>18</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>180</v>
       </c>
       <c r="I12" s="8">
         <v>1001</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="M12" s="25" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="G14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I14" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="I14" s="2">
+        <v>2001</v>
+      </c>
       <c r="J14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="G15" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I15" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="I15" s="8">
+        <v>1001</v>
+      </c>
       <c r="J15" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="M15" s="25" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>52</v>
+        <v>31</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>35</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="G16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I16" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="I16" s="2">
+        <v>3001</v>
+      </c>
       <c r="J16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="M16" s="22" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="I17" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H17" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>142</v>
+      </c>
       <c r="J17" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L17" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="22" t="s">
         <v>22</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I18" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="J18" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="25" t="s">
         <v>22</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I19" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H19" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="J19" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="J20" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="I21" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H21" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="I21" s="8">
+        <v>10</v>
+      </c>
       <c r="J21" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="22" t="s">
         <v>22</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I22" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>146</v>
+      </c>
       <c r="J22" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="F23" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="I23" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H23" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="I23" s="21">
+        <v>250</v>
+      </c>
       <c r="J23" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="E24" s="2" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I24" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>147</v>
+      </c>
       <c r="J24" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I25" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="H25" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="I25" s="23">
+        <v>46037</v>
+      </c>
       <c r="J25" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I26" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H26" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="I26" s="14">
+        <v>46068</v>
+      </c>
       <c r="J26" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>81</v>
+        <v>51</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>52</v>
       </c>
       <c r="E28" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F28" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="G28" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I28" s="8"/>
+        <v>17</v>
+      </c>
+      <c r="H28" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="I28" s="8">
+        <v>4001</v>
+      </c>
       <c r="J28" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>83</v>
+        <v>50</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="G29" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I29" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1002</v>
+      </c>
       <c r="J29" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M29" s="22" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E30" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F30" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="G30" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I30" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H30" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="I30" s="8">
+        <v>5001</v>
+      </c>
       <c r="J30" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="K30" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L30" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" s="25" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I31" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="I31" s="2">
+        <v>12.99</v>
+      </c>
       <c r="J31" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="I32" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H32" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="I32" s="8">
+        <v>8</v>
+      </c>
       <c r="J32" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I33" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="I33" s="24">
+        <v>275.5</v>
+      </c>
       <c r="J33" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="I34" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H34" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="I34" s="25" t="s">
+        <v>148</v>
+      </c>
       <c r="J34" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="35" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>22</v>
+        <v>61</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>25</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I35" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H35" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="I35" s="2">
+        <v>10001</v>
+      </c>
       <c r="J35" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="36" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="I36" s="14"/>
+        <v>18</v>
+      </c>
+      <c r="H36" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="I36" s="26" t="s">
+        <v>149</v>
+      </c>
       <c r="J36" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="37" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>22</v>
+        <v>64</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>47</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I37" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H37" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="I37" s="22" t="s">
+        <v>150</v>
+      </c>
       <c r="J37" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L37" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="38" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="20"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="22"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
     </row>
     <row r="39" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="E39" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F39" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="G39" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="H39" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="I39" s="8">
+        <v>4001</v>
+      </c>
+      <c r="J39" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L39" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="25" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="40" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="G40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="H40" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="I40" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J40" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L40" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="M40" s="22" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="41" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="I41" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H41" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="I41" s="21">
+        <v>240</v>
+      </c>
       <c r="J41" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L41" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="42" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="18"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
     </row>
     <row r="43" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="G43" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I43" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="H43" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="I43" s="2">
+        <v>7001</v>
+      </c>
       <c r="J43" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="44" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="E44" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F44" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="G44" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="I44" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H44" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="I44" s="8">
+        <v>4001</v>
+      </c>
       <c r="J44" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="K44" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L44" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="25" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="45" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E45" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="22" t="s">
         <v>22</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I45" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H45" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="I45" s="22" t="s">
+        <v>151</v>
+      </c>
       <c r="J45" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="46" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="I46" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H46" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="I46" s="25" t="s">
+        <v>152</v>
+      </c>
       <c r="J46" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="47" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I47" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H47" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="I47" s="14">
+        <v>46038</v>
+      </c>
       <c r="J47" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="48" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="20"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="22"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="19"/>
+      <c r="M48" s="19"/>
     </row>
     <row r="49" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="E49" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F49" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="G49" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="I49" s="8"/>
+        <v>17</v>
+      </c>
+      <c r="H49" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="I49" s="8">
+        <v>3001</v>
+      </c>
       <c r="J49" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="K49" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="M49" s="25" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="50" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I50" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H50" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="I50" s="22" t="s">
+        <v>153</v>
+      </c>
       <c r="J50" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="51" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E51" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F51" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="G51" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H51" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="I51" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H51" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="I51" s="8">
+        <v>1001</v>
+      </c>
       <c r="J51" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="K51" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L51" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="M51" s="25" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="52" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" s="22" t="s">
         <v>22</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I52" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H52" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="I52" s="22" t="s">
+        <v>142</v>
+      </c>
       <c r="J52" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="53" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H53" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="I53" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H53" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="I53" s="25" t="s">
+        <v>143</v>
+      </c>
       <c r="J53" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M53" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="54" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I54" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H54" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="I54" s="22" t="s">
+        <v>144</v>
+      </c>
       <c r="J54" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="55" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H55" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="I55" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H55" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="I55" s="8">
+        <v>10</v>
+      </c>
       <c r="J55" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="56" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I56" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H56" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="I56" s="22" t="s">
+        <v>154</v>
+      </c>
       <c r="J56" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="57" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E57" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E57" s="25" t="s">
         <v>22</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H57" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="I57" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H57" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="I57" s="25" t="s">
+        <v>156</v>
+      </c>
       <c r="J57" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="58" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="I58" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L58" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
+      <c r="M58" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="59" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="I59" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="H59" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="I59" s="23">
+        <v>46032</v>
+      </c>
       <c r="J59" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="60" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="18"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
-      <c r="H60" s="18"/>
-      <c r="I60" s="23"/>
-      <c r="J60" s="18"/>
-      <c r="K60" s="18"/>
-      <c r="L60" s="19"/>
-      <c r="M60" s="19"/>
+      <c r="A60" s="15"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="20"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
     </row>
     <row r="61" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="E61" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F61" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="G61" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I61" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="H61" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="I61" s="2">
+        <v>9001</v>
+      </c>
       <c r="J61" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="K61" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L61" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="M61" s="22" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="62" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="D62" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="F62" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F62" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="G62" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H62" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="I62" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H62" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="I62" s="8">
+        <v>1002</v>
+      </c>
       <c r="J62" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K62" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="K62" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L62" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" s="25" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="63" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E63" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="22" t="s">
         <v>22</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I63" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H63" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="I63" s="22" t="s">
+        <v>157</v>
+      </c>
       <c r="J63" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="64" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E64" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" s="25" t="s">
         <v>22</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="I64" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H64" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="I64" s="25" t="s">
+        <v>158</v>
+      </c>
       <c r="J64" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K64" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L64" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M64" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="65" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>22</v>
+        <v>86</v>
+      </c>
+      <c r="E65" s="22" t="s">
+        <v>60</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I65" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H65" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="I65" s="22" t="s">
+        <v>159</v>
+      </c>
       <c r="J65" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="66" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="I66" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H66" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="I66" s="12" t="s">
+        <v>160</v>
+      </c>
       <c r="J66" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L66" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M66" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="67" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>22</v>
+        <v>87</v>
+      </c>
+      <c r="E67" s="22" t="s">
+        <v>47</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I67" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H67" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="I67" s="22" t="s">
+        <v>161</v>
+      </c>
       <c r="J67" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="68" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="E68" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="I68" s="8">
+        <v>4001</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K68" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="F68" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K68" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
+      <c r="L68" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M68" s="25" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="69" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>22</v>
+        <v>88</v>
+      </c>
+      <c r="E69" s="22" t="s">
+        <v>60</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I69" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H69" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="I69" s="22" t="s">
+        <v>162</v>
+      </c>
       <c r="J69" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="70" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>22</v>
+        <v>89</v>
+      </c>
+      <c r="E70" s="25" t="s">
+        <v>47</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I70" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="H70" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="I70" s="25" t="s">
+        <v>21</v>
+      </c>
       <c r="J70" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L70" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M70" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="71" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="2"/>
@@ -10431,10 +10816,11 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I5" r:id="rId1" xr:uid="{67BDF40E-122B-43EF-BE5B-F2839AAA46BB}"/>
+    <hyperlink ref="I66" r:id="rId2" xr:uid="{6F02E1ED-BE75-4129-B1E8-DEA4E6B3FEB3}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -10443,194 +10829,195 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F500"/>
+  <dimension ref="A1:F498"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" customWidth="1"/>
-    <col min="3" max="4" width="16.77734375" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>164</v>
+        <v>92</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>165</v>
+        <v>93</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>166</v>
+        <v>94</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>167</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>170</v>
+        <v>98</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>171</v>
+        <v>99</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>174</v>
+      <c r="A3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>179</v>
+      <c r="A4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>181</v>
+      <c r="A5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>185</v>
+      <c r="C8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>187</v>
+      <c r="A9" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10650,68 +11037,68 @@
       <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
@@ -10793,7 +11180,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -10801,7 +11188,7 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -14544,22 +14931,6 @@
       <c r="D498" s="4"/>
       <c r="E498" s="4"/>
       <c r="F498" s="4"/>
-    </row>
-    <row r="499" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A499" s="3"/>
-      <c r="B499" s="3"/>
-      <c r="C499" s="3"/>
-      <c r="D499" s="3"/>
-      <c r="E499" s="3"/>
-      <c r="F499" s="3"/>
-    </row>
-    <row r="500" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A500" s="4"/>
-      <c r="B500" s="4"/>
-      <c r="C500" s="4"/>
-      <c r="D500" s="4"/>
-      <c r="E500" s="4"/>
-      <c r="F500" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14586,66 +14957,66 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>109</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>191</v>
+        <v>110</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>193</v>
+        <v>112</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>194</v>
+        <v>113</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>195</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>196</v>
+        <v>115</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>198</v>
+        <v>117</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>200</v>
+        <v>119</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>202</v>
+        <v>121</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>203</v>
+        <v>122</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>204</v>
+        <v>123</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>205</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
@@ -14766,30 +15137,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>206</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>207</v>
+        <v>126</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>208</v>
+        <v>127</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>192</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>209</v>
+        <v>128</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>210</v>
+        <v>129</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>211</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -14861,24 +15232,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>213</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>214</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>216</v>
+        <v>135</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>217</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
